--- a/artfynd/A 50182-2025 artfynd.xlsx
+++ b/artfynd/A 50182-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ4"/>
+  <dimension ref="A1:AZ30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -680,10 +680,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129805482</v>
+        <v>136876156</v>
       </c>
       <c r="B2" t="n">
-        <v>57953</v>
+        <v>79142</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,37 +691,37 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100109</v>
+        <v>353</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Råberget ö, Hjd</t>
+          <t>Neder-Dammtjärnen, Neder-Dammtjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>421820</v>
+        <v>421423</v>
       </c>
       <c r="R2" t="n">
-        <v>6962017</v>
+        <v>6962110</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -745,17 +745,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-11-22</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2025-11-22</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -770,27 +765,27 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
       <c r="AZ2" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129805482</t>
+          <t>https://artportalen.se/Sighting/136876156</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129805483</v>
+        <v>136876745</v>
       </c>
       <c r="B3" t="n">
-        <v>57953</v>
+        <v>92384</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -798,37 +793,37 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>658</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Råberget ö, Hjd</t>
+          <t>Neder-Dammtjärnen, Neder-Dammtjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>421818</v>
+        <v>421587</v>
       </c>
       <c r="R3" t="n">
-        <v>6961973</v>
+        <v>6962137</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -852,17 +847,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-11-22</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2025-11-22</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -877,27 +867,27 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129805483</t>
+          <t>https://artportalen.se/Sighting/136876745</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129805484</v>
+        <v>136876592</v>
       </c>
       <c r="B4" t="n">
-        <v>57953</v>
+        <v>92113</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -905,37 +895,37 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Råberget ö, Hjd</t>
+          <t>Neder-Dammtjärnen, Neder-Dammtjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>421780</v>
+        <v>421538</v>
       </c>
       <c r="R4" t="n">
-        <v>6961939</v>
+        <v>6962088</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -959,17 +949,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-11-22</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2025-11-22</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -984,18 +969,2765 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
       <c r="AZ4" t="inlineStr">
         <is>
+          <t>https://artportalen.se/Sighting/136876592</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>136876789</v>
+      </c>
+      <c r="B5" t="n">
+        <v>92113</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Neder-Dammtjärnen, Neder-Dammtjärnen, Hjd</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>421587</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6962146</v>
+      </c>
+      <c r="S5" t="n">
+        <v>15</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Storsjö</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136876789</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>136876174</v>
+      </c>
+      <c r="B6" t="n">
+        <v>79476</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Neder-Dammtjärnen, Neder-Dammtjärnen, Hjd</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>421418</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6962123</v>
+      </c>
+      <c r="S6" t="n">
+        <v>15</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Storsjö</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136876174</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>136876238</v>
+      </c>
+      <c r="B7" t="n">
+        <v>79476</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Neder-Dammtjärnen, Neder-Dammtjärnen, Hjd</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>421418</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6962138</v>
+      </c>
+      <c r="S7" t="n">
+        <v>15</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Storsjö</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136876238</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>136876450</v>
+      </c>
+      <c r="B8" t="n">
+        <v>79476</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Neder-Dammtjärnen, Neder-Dammtjärnen, Hjd</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>421513</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6962123</v>
+      </c>
+      <c r="S8" t="n">
+        <v>15</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Storsjö</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136876450</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>136877256</v>
+      </c>
+      <c r="B9" t="n">
+        <v>79476</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Neder-Dammtjärnen, Neder-Dammtjärnen, Hjd</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>421674</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6962007</v>
+      </c>
+      <c r="S9" t="n">
+        <v>15</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Storsjö</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136877256</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>136876565</v>
+      </c>
+      <c r="B10" t="n">
+        <v>78879</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>6437</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Blanksvart spiklav</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Calicium denigratum</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Vain.) Tibell</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Neder-Dammtjärnen, Neder-Dammtjärnen, Hjd</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>421522</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6962095</v>
+      </c>
+      <c r="S10" t="n">
+        <v>15</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Storsjö</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136876565</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>136875679</v>
+      </c>
+      <c r="B11" t="n">
+        <v>80095</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Över-Dammtjärnen, Över-Dammtjärnen, Hjd</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>421731</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6961870</v>
+      </c>
+      <c r="S11" t="n">
+        <v>15</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Storsjö</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136875679</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>136876728</v>
+      </c>
+      <c r="B12" t="n">
+        <v>80095</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Neder-Dammtjärnen, Neder-Dammtjärnen, Hjd</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>421575</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6962149</v>
+      </c>
+      <c r="S12" t="n">
+        <v>15</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Storsjö</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136876728</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>136875760</v>
+      </c>
+      <c r="B13" t="n">
+        <v>80595</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>6461</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Norrlandslav</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Nephroma arcticum</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(L.) Torss.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Över-Dammtjärnen, Över-Dammtjärnen, Hjd</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>421670</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6961834</v>
+      </c>
+      <c r="S13" t="n">
+        <v>15</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Storsjö</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136875760</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>136876098</v>
+      </c>
+      <c r="B14" t="n">
+        <v>80595</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>6461</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Norrlandslav</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Nephroma arcticum</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(L.) Torss.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Neder-Dammtjärnen, Neder-Dammtjärnen, Hjd</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>421474</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6962089</v>
+      </c>
+      <c r="S14" t="n">
+        <v>15</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Storsjö</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136876098</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>136876326</v>
+      </c>
+      <c r="B15" t="n">
+        <v>78480</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>6487</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Blågrå svartspik</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Chaenothecopsis fennica</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(Laurila) Tibell</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Neder-Dammtjärnen, Neder-Dammtjärnen, Hjd</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>421458</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6962164</v>
+      </c>
+      <c r="S15" t="n">
+        <v>15</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Storsjö</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136876326</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>129805482</v>
+      </c>
+      <c r="B16" t="n">
+        <v>57953</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Råberget ö, Hjd</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>421820</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6962017</v>
+      </c>
+      <c r="S16" t="n">
+        <v>10</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Storsjö</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2025-11-22</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2025-11-22</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129805482</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>129805483</v>
+      </c>
+      <c r="B17" t="n">
+        <v>57953</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Råberget ö, Hjd</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>421818</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6961973</v>
+      </c>
+      <c r="S17" t="n">
+        <v>10</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Storsjö</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2025-11-22</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2025-11-22</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129805483</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>129805484</v>
+      </c>
+      <c r="B18" t="n">
+        <v>57953</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Råberget ö, Hjd</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>421780</v>
+      </c>
+      <c r="R18" t="n">
+        <v>6961939</v>
+      </c>
+      <c r="S18" t="n">
+        <v>10</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Storsjö</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2025-11-22</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2025-11-22</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
           <t>https://artportalen.se/Sighting/129805484</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>136875592</v>
+      </c>
+      <c r="B19" t="n">
+        <v>58008</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Över-Dammtjärnen, Över-Dammtjärnen, Hjd</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>421757</v>
+      </c>
+      <c r="R19" t="n">
+        <v>6961899</v>
+      </c>
+      <c r="S19" t="n">
+        <v>15</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Storsjö</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Ringhack gran</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136875592</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>136876019</v>
+      </c>
+      <c r="B20" t="n">
+        <v>58008</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Neder-Dammtjärnen, Neder-Dammtjärnen, Hjd</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>421451</v>
+      </c>
+      <c r="R20" t="n">
+        <v>6961996</v>
+      </c>
+      <c r="S20" t="n">
+        <v>15</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Storsjö</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Ringhack, tall</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136876019</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>136876076</v>
+      </c>
+      <c r="B21" t="n">
+        <v>58008</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Neder-Dammtjärnen, Neder-Dammtjärnen, Hjd</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>421474</v>
+      </c>
+      <c r="R21" t="n">
+        <v>6962095</v>
+      </c>
+      <c r="S21" t="n">
+        <v>15</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Storsjö</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136876076</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>136876706</v>
+      </c>
+      <c r="B22" t="n">
+        <v>58008</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Neder-Dammtjärnen, Neder-Dammtjärnen, Hjd</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>421583</v>
+      </c>
+      <c r="R22" t="n">
+        <v>6962122</v>
+      </c>
+      <c r="S22" t="n">
+        <v>15</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Storsjö</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136876706</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>136876886</v>
+      </c>
+      <c r="B23" t="n">
+        <v>58008</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Neder-Dammtjärnen, Neder-Dammtjärnen, Hjd</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>421615</v>
+      </c>
+      <c r="R23" t="n">
+        <v>6962100</v>
+      </c>
+      <c r="S23" t="n">
+        <v>15</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Storsjö</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Ringhack, gran</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136876886</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>136877183</v>
+      </c>
+      <c r="B24" t="n">
+        <v>58008</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Neder-Dammtjärnen, Neder-Dammtjärnen, Hjd</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>421678</v>
+      </c>
+      <c r="R24" t="n">
+        <v>6962031</v>
+      </c>
+      <c r="S24" t="n">
+        <v>15</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Storsjö</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136877183</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>136877310</v>
+      </c>
+      <c r="B25" t="n">
+        <v>58008</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Neder-Dammtjärnen, Neder-Dammtjärnen, Hjd</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>421685</v>
+      </c>
+      <c r="R25" t="n">
+        <v>6961978</v>
+      </c>
+      <c r="S25" t="n">
+        <v>15</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Storsjö</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Ringhack, gran</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136877310</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>136877341</v>
+      </c>
+      <c r="B26" t="n">
+        <v>58008</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Över-Dammtjärnen, Över-Dammtjärnen, Hjd</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>421710</v>
+      </c>
+      <c r="R26" t="n">
+        <v>6961940</v>
+      </c>
+      <c r="S26" t="n">
+        <v>15</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Storsjö</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>Ringhack, tall</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136877341</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>136875986</v>
+      </c>
+      <c r="B27" t="n">
+        <v>58112</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>103031</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Lavskrika</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Perisoreus infaustus</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Neder-Dammtjärnen, Neder-Dammtjärnen, Hjd</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>421448</v>
+      </c>
+      <c r="R27" t="n">
+        <v>6961988</v>
+      </c>
+      <c r="S27" t="n">
+        <v>15</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Storsjö</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136875986</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>136876734</v>
+      </c>
+      <c r="B28" t="n">
+        <v>80066</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>229821</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Vedflamlav</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Ramboldia elabens</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Neder-Dammtjärnen, Neder-Dammtjärnen, Hjd</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>421576</v>
+      </c>
+      <c r="R28" t="n">
+        <v>6962161</v>
+      </c>
+      <c r="S28" t="n">
+        <v>15</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Storsjö</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="AD28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136876734</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>136875725</v>
+      </c>
+      <c r="B29" t="n">
+        <v>79499</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>260591</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Talltagel</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Bryoria fremontii</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>(Tuck.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>Över-Dammtjärnen, Över-Dammtjärnen, Hjd</t>
+        </is>
+      </c>
+      <c r="Q29" t="n">
+        <v>421716</v>
+      </c>
+      <c r="R29" t="n">
+        <v>6961831</v>
+      </c>
+      <c r="S29" t="n">
+        <v>15</v>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Storsjö</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="AD29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT29" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX29" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136875725</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>136876573</v>
+      </c>
+      <c r="B30" t="n">
+        <v>79499</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>260591</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Talltagel</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Bryoria fremontii</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>(Tuck.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>Neder-Dammtjärnen, Neder-Dammtjärnen, Hjd</t>
+        </is>
+      </c>
+      <c r="Q30" t="n">
+        <v>421524</v>
+      </c>
+      <c r="R30" t="n">
+        <v>6962087</v>
+      </c>
+      <c r="S30" t="n">
+        <v>15</v>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Storsjö</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="AD30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT30" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX30" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136876573</t>
         </is>
       </c>
     </row>
@@ -1004,6 +3736,32 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 50182-2025 artfynd.xlsx
+++ b/artfynd/A 50182-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ30"/>
+  <dimension ref="A1:AZ31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1598,10 +1598,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>136875679</v>
+        <v>136875998</v>
       </c>
       <c r="B11" t="n">
-        <v>80095</v>
+        <v>83463</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1609,34 +1609,37 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6453</v>
+        <v>6440</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Över-Dammtjärnen, Över-Dammtjärnen, Hjd</t>
+          <t>Neder-Dammtjärnen, Neder-Dammtjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>421731</v>
+        <v>421450</v>
       </c>
       <c r="R11" t="n">
-        <v>6961870</v>
+        <v>6961994</v>
       </c>
       <c r="S11" t="n">
         <v>15</v>
@@ -1677,6 +1680,7 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
+      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1694,13 +1698,13 @@
       <c r="AY11" t="inlineStr"/>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136875679</t>
+          <t>https://artportalen.se/Sighting/136875998</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>136876728</v>
+        <v>136875679</v>
       </c>
       <c r="B12" t="n">
         <v>80095</v>
@@ -1731,14 +1735,14 @@
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Neder-Dammtjärnen, Neder-Dammtjärnen, Hjd</t>
+          <t>Över-Dammtjärnen, Över-Dammtjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>421575</v>
+        <v>421731</v>
       </c>
       <c r="R12" t="n">
-        <v>6962149</v>
+        <v>6961870</v>
       </c>
       <c r="S12" t="n">
         <v>15</v>
@@ -1796,51 +1800,51 @@
       <c r="AY12" t="inlineStr"/>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136876728</t>
+          <t>https://artportalen.se/Sighting/136875679</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>136875760</v>
+        <v>136876728</v>
       </c>
       <c r="B13" t="n">
-        <v>80595</v>
+        <v>80095</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6461</v>
+        <v>6453</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Över-Dammtjärnen, Över-Dammtjärnen, Hjd</t>
+          <t>Neder-Dammtjärnen, Neder-Dammtjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>421670</v>
+        <v>421575</v>
       </c>
       <c r="R13" t="n">
-        <v>6961834</v>
+        <v>6962149</v>
       </c>
       <c r="S13" t="n">
         <v>15</v>
@@ -1898,13 +1902,13 @@
       <c r="AY13" t="inlineStr"/>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136875760</t>
+          <t>https://artportalen.se/Sighting/136876728</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>136876098</v>
+        <v>136875760</v>
       </c>
       <c r="B14" t="n">
         <v>80595</v>
@@ -1935,14 +1939,14 @@
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Neder-Dammtjärnen, Neder-Dammtjärnen, Hjd</t>
+          <t>Över-Dammtjärnen, Över-Dammtjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>421474</v>
+        <v>421670</v>
       </c>
       <c r="R14" t="n">
-        <v>6962089</v>
+        <v>6961834</v>
       </c>
       <c r="S14" t="n">
         <v>15</v>
@@ -2000,38 +2004,38 @@
       <c r="AY14" t="inlineStr"/>
       <c r="AZ14" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136876098</t>
+          <t>https://artportalen.se/Sighting/136875760</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>136876326</v>
+        <v>136876098</v>
       </c>
       <c r="B15" t="n">
-        <v>78480</v>
+        <v>80595</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6487</v>
+        <v>6461</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2041,10 +2045,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>421458</v>
+        <v>421474</v>
       </c>
       <c r="R15" t="n">
-        <v>6962164</v>
+        <v>6962089</v>
       </c>
       <c r="S15" t="n">
         <v>15</v>
@@ -2102,16 +2106,16 @@
       <c r="AY15" t="inlineStr"/>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136876326</t>
+          <t>https://artportalen.se/Sighting/136876098</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129805482</v>
+        <v>136876326</v>
       </c>
       <c r="B16" t="n">
-        <v>57953</v>
+        <v>78480</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2119,37 +2123,37 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100109</v>
+        <v>6487</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Råberget ö, Hjd</t>
+          <t>Neder-Dammtjärnen, Neder-Dammtjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>421820</v>
+        <v>421458</v>
       </c>
       <c r="R16" t="n">
-        <v>6962017</v>
+        <v>6962164</v>
       </c>
       <c r="S16" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2173,17 +2177,12 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2025-11-22</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2025-11-22</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2198,24 +2197,24 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129805482</t>
+          <t>https://artportalen.se/Sighting/136876326</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129805483</v>
+        <v>129805482</v>
       </c>
       <c r="B17" t="n">
         <v>57953</v>
@@ -2250,10 +2249,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>421818</v>
+        <v>421820</v>
       </c>
       <c r="R17" t="n">
-        <v>6961973</v>
+        <v>6962017</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2290,7 +2289,7 @@
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2316,13 +2315,13 @@
       <c r="AY17" t="inlineStr"/>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129805483</t>
+          <t>https://artportalen.se/Sighting/129805482</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129805484</v>
+        <v>129805483</v>
       </c>
       <c r="B18" t="n">
         <v>57953</v>
@@ -2357,10 +2356,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>421780</v>
+        <v>421818</v>
       </c>
       <c r="R18" t="n">
-        <v>6961939</v>
+        <v>6961973</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2397,7 +2396,7 @@
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2423,16 +2422,16 @@
       <c r="AY18" t="inlineStr"/>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129805484</t>
+          <t>https://artportalen.se/Sighting/129805483</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>136875592</v>
+        <v>129805484</v>
       </c>
       <c r="B19" t="n">
-        <v>58008</v>
+        <v>57953</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2458,24 +2457,19 @@
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Över-Dammtjärnen, Över-Dammtjärnen, Hjd</t>
+          <t>Råberget ö, Hjd</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>421757</v>
+        <v>421780</v>
       </c>
       <c r="R19" t="n">
-        <v>6961899</v>
+        <v>6961939</v>
       </c>
       <c r="S19" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2499,17 +2493,17 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2025-11-22</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2025-11-22</t>
         </is>
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>Ringhack gran</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2524,24 +2518,24 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
       <c r="AZ19" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136875592</t>
+          <t>https://artportalen.se/Sighting/129805484</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>136876019</v>
+        <v>136875592</v>
       </c>
       <c r="B20" t="n">
         <v>58008</v>
@@ -2577,14 +2571,14 @@
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Neder-Dammtjärnen, Neder-Dammtjärnen, Hjd</t>
+          <t>Över-Dammtjärnen, Över-Dammtjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>421451</v>
+        <v>421757</v>
       </c>
       <c r="R20" t="n">
-        <v>6961996</v>
+        <v>6961899</v>
       </c>
       <c r="S20" t="n">
         <v>15</v>
@@ -2621,7 +2615,7 @@
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>Ringhack, tall</t>
+          <t>Ringhack gran</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2647,13 +2641,13 @@
       <c r="AY20" t="inlineStr"/>
       <c r="AZ20" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136876019</t>
+          <t>https://artportalen.se/Sighting/136875592</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>136876076</v>
+        <v>136876019</v>
       </c>
       <c r="B21" t="n">
         <v>58008</v>
@@ -2684,7 +2678,7 @@
       <c r="I21" t="inlineStr"/>
       <c r="M21" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
@@ -2693,10 +2687,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>421474</v>
+        <v>421451</v>
       </c>
       <c r="R21" t="n">
-        <v>6962095</v>
+        <v>6961996</v>
       </c>
       <c r="S21" t="n">
         <v>15</v>
@@ -2733,7 +2727,7 @@
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack, tall</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2759,13 +2753,13 @@
       <c r="AY21" t="inlineStr"/>
       <c r="AZ21" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136876076</t>
+          <t>https://artportalen.se/Sighting/136876019</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>136876706</v>
+        <v>136876076</v>
       </c>
       <c r="B22" t="n">
         <v>58008</v>
@@ -2796,7 +2790,7 @@
       <c r="I22" t="inlineStr"/>
       <c r="M22" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
@@ -2805,10 +2799,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>421583</v>
+        <v>421474</v>
       </c>
       <c r="R22" t="n">
-        <v>6962122</v>
+        <v>6962095</v>
       </c>
       <c r="S22" t="n">
         <v>15</v>
@@ -2845,7 +2839,7 @@
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>Färska ringhack</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2871,13 +2865,13 @@
       <c r="AY22" t="inlineStr"/>
       <c r="AZ22" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136876706</t>
+          <t>https://artportalen.se/Sighting/136876076</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>136876886</v>
+        <v>136876706</v>
       </c>
       <c r="B23" t="n">
         <v>58008</v>
@@ -2908,7 +2902,7 @@
       <c r="I23" t="inlineStr"/>
       <c r="M23" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
@@ -2917,10 +2911,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>421615</v>
+        <v>421583</v>
       </c>
       <c r="R23" t="n">
-        <v>6962100</v>
+        <v>6962122</v>
       </c>
       <c r="S23" t="n">
         <v>15</v>
@@ -2957,7 +2951,7 @@
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>Ringhack, gran</t>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -2983,13 +2977,13 @@
       <c r="AY23" t="inlineStr"/>
       <c r="AZ23" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136876886</t>
+          <t>https://artportalen.se/Sighting/136876706</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>136877183</v>
+        <v>136876886</v>
       </c>
       <c r="B24" t="n">
         <v>58008</v>
@@ -3018,14 +3012,9 @@
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="L24" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
@@ -3034,10 +3023,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>421678</v>
+        <v>421615</v>
       </c>
       <c r="R24" t="n">
-        <v>6962031</v>
+        <v>6962100</v>
       </c>
       <c r="S24" t="n">
         <v>15</v>
@@ -3072,6 +3061,11 @@
           <t>2026-09-26</t>
         </is>
       </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Ringhack, gran</t>
+        </is>
+      </c>
       <c r="AD24" t="b">
         <v>0</v>
       </c>
@@ -3095,13 +3089,13 @@
       <c r="AY24" t="inlineStr"/>
       <c r="AZ24" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136877183</t>
+          <t>https://artportalen.se/Sighting/136876886</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>136877310</v>
+        <v>136877183</v>
       </c>
       <c r="B25" t="n">
         <v>58008</v>
@@ -3130,9 +3124,14 @@
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
@@ -3141,10 +3140,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>421685</v>
+        <v>421678</v>
       </c>
       <c r="R25" t="n">
-        <v>6961978</v>
+        <v>6962031</v>
       </c>
       <c r="S25" t="n">
         <v>15</v>
@@ -3179,11 +3178,6 @@
           <t>2026-09-26</t>
         </is>
       </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>Ringhack, gran</t>
-        </is>
-      </c>
       <c r="AD25" t="b">
         <v>0</v>
       </c>
@@ -3207,13 +3201,13 @@
       <c r="AY25" t="inlineStr"/>
       <c r="AZ25" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136877310</t>
+          <t>https://artportalen.se/Sighting/136877183</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>136877341</v>
+        <v>136877310</v>
       </c>
       <c r="B26" t="n">
         <v>58008</v>
@@ -3244,19 +3238,19 @@
       <c r="I26" t="inlineStr"/>
       <c r="M26" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Över-Dammtjärnen, Över-Dammtjärnen, Hjd</t>
+          <t>Neder-Dammtjärnen, Neder-Dammtjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>421710</v>
+        <v>421685</v>
       </c>
       <c r="R26" t="n">
-        <v>6961940</v>
+        <v>6961978</v>
       </c>
       <c r="S26" t="n">
         <v>15</v>
@@ -3293,7 +3287,7 @@
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>Ringhack, tall</t>
+          <t>Ringhack, gran</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3319,16 +3313,16 @@
       <c r="AY26" t="inlineStr"/>
       <c r="AZ26" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136877341</t>
+          <t>https://artportalen.se/Sighting/136877310</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>136875986</v>
+        <v>136877341</v>
       </c>
       <c r="B27" t="n">
-        <v>58112</v>
+        <v>58008</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3336,16 +3330,16 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>103031</v>
+        <v>100109</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -3354,16 +3348,21 @@
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Neder-Dammtjärnen, Neder-Dammtjärnen, Hjd</t>
+          <t>Över-Dammtjärnen, Över-Dammtjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>421448</v>
+        <v>421710</v>
       </c>
       <c r="R27" t="n">
-        <v>6961988</v>
+        <v>6961940</v>
       </c>
       <c r="S27" t="n">
         <v>15</v>
@@ -3398,6 +3397,11 @@
           <t>2026-09-26</t>
         </is>
       </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>Ringhack, tall</t>
+        </is>
+      </c>
       <c r="AD27" t="b">
         <v>0</v>
       </c>
@@ -3421,16 +3425,16 @@
       <c r="AY27" t="inlineStr"/>
       <c r="AZ27" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136875986</t>
+          <t>https://artportalen.se/Sighting/136877341</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>136876734</v>
+        <v>136875986</v>
       </c>
       <c r="B28" t="n">
-        <v>80066</v>
+        <v>58112</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3438,21 +3442,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>229821</v>
+        <v>103031</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3462,10 +3466,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>421576</v>
+        <v>421448</v>
       </c>
       <c r="R28" t="n">
-        <v>6962161</v>
+        <v>6961988</v>
       </c>
       <c r="S28" t="n">
         <v>15</v>
@@ -3523,16 +3527,16 @@
       <c r="AY28" t="inlineStr"/>
       <c r="AZ28" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136876734</t>
+          <t>https://artportalen.se/Sighting/136875986</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>136875725</v>
+        <v>136876734</v>
       </c>
       <c r="B29" t="n">
-        <v>79499</v>
+        <v>80066</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3540,34 +3544,34 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>260591</v>
+        <v>229821</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Talltagel</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Bryoria fremontii</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Tuck.) Brodo &amp; D.Hawksw.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Över-Dammtjärnen, Över-Dammtjärnen, Hjd</t>
+          <t>Neder-Dammtjärnen, Neder-Dammtjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>421716</v>
+        <v>421576</v>
       </c>
       <c r="R29" t="n">
-        <v>6961831</v>
+        <v>6962161</v>
       </c>
       <c r="S29" t="n">
         <v>15</v>
@@ -3625,13 +3629,13 @@
       <c r="AY29" t="inlineStr"/>
       <c r="AZ29" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136875725</t>
+          <t>https://artportalen.se/Sighting/136876734</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>136876573</v>
+        <v>136875725</v>
       </c>
       <c r="B30" t="n">
         <v>79499</v>
@@ -3662,14 +3666,14 @@
       <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Neder-Dammtjärnen, Neder-Dammtjärnen, Hjd</t>
+          <t>Över-Dammtjärnen, Över-Dammtjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>421524</v>
+        <v>421716</v>
       </c>
       <c r="R30" t="n">
-        <v>6962087</v>
+        <v>6961831</v>
       </c>
       <c r="S30" t="n">
         <v>15</v>
@@ -3726,6 +3730,108 @@
       </c>
       <c r="AY30" t="inlineStr"/>
       <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136875725</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>136876573</v>
+      </c>
+      <c r="B31" t="n">
+        <v>79499</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>260591</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Talltagel</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Bryoria fremontii</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>(Tuck.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>Neder-Dammtjärnen, Neder-Dammtjärnen, Hjd</t>
+        </is>
+      </c>
+      <c r="Q31" t="n">
+        <v>421524</v>
+      </c>
+      <c r="R31" t="n">
+        <v>6962087</v>
+      </c>
+      <c r="S31" t="n">
+        <v>15</v>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>Storsjö</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="AD31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT31" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX31" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/136876573</t>
         </is>
@@ -3762,6 +3868,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 50182-2025 artfynd.xlsx
+++ b/artfynd/A 50182-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136876156</v>
       </c>
       <c r="B2" t="n">
-        <v>79142</v>
+        <v>79146</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>136876745</v>
       </c>
       <c r="B3" t="n">
-        <v>92384</v>
+        <v>92386</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         <v>136876592</v>
       </c>
       <c r="B4" t="n">
-        <v>92113</v>
+        <v>92115</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
         <v>136876789</v>
       </c>
       <c r="B5" t="n">
-        <v>92113</v>
+        <v>92115</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1091,7 +1091,7 @@
         <v>136876174</v>
       </c>
       <c r="B6" t="n">
-        <v>79476</v>
+        <v>79480</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1193,7 +1193,7 @@
         <v>136876238</v>
       </c>
       <c r="B7" t="n">
-        <v>79476</v>
+        <v>79480</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1295,7 +1295,7 @@
         <v>136876450</v>
       </c>
       <c r="B8" t="n">
-        <v>79476</v>
+        <v>79480</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1397,7 +1397,7 @@
         <v>136877256</v>
       </c>
       <c r="B9" t="n">
-        <v>79476</v>
+        <v>79480</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1499,7 +1499,7 @@
         <v>136876565</v>
       </c>
       <c r="B10" t="n">
-        <v>78879</v>
+        <v>78883</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1601,7 +1601,7 @@
         <v>136875998</v>
       </c>
       <c r="B11" t="n">
-        <v>83463</v>
+        <v>83467</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1707,7 +1707,7 @@
         <v>136875679</v>
       </c>
       <c r="B12" t="n">
-        <v>80095</v>
+        <v>80099</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1809,7 +1809,7 @@
         <v>136876728</v>
       </c>
       <c r="B13" t="n">
-        <v>80095</v>
+        <v>80099</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1911,7 +1911,7 @@
         <v>136875760</v>
       </c>
       <c r="B14" t="n">
-        <v>80595</v>
+        <v>80599</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2013,7 +2013,7 @@
         <v>136876098</v>
       </c>
       <c r="B15" t="n">
-        <v>80595</v>
+        <v>80599</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -3536,7 +3536,7 @@
         <v>136876734</v>
       </c>
       <c r="B29" t="n">
-        <v>80066</v>
+        <v>80070</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3638,7 +3638,7 @@
         <v>136875725</v>
       </c>
       <c r="B30" t="n">
-        <v>79499</v>
+        <v>79503</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3740,7 +3740,7 @@
         <v>136876573</v>
       </c>
       <c r="B31" t="n">
-        <v>79499</v>
+        <v>79503</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>

--- a/artfynd/A 50182-2025 artfynd.xlsx
+++ b/artfynd/A 50182-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136876156</v>
       </c>
       <c r="B2" t="n">
-        <v>79146</v>
+        <v>79148</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>136876745</v>
       </c>
       <c r="B3" t="n">
-        <v>92386</v>
+        <v>92388</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         <v>136876592</v>
       </c>
       <c r="B4" t="n">
-        <v>92115</v>
+        <v>92117</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
         <v>136876789</v>
       </c>
       <c r="B5" t="n">
-        <v>92115</v>
+        <v>92117</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1091,7 +1091,7 @@
         <v>136876174</v>
       </c>
       <c r="B6" t="n">
-        <v>79480</v>
+        <v>79482</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1193,7 +1193,7 @@
         <v>136876238</v>
       </c>
       <c r="B7" t="n">
-        <v>79480</v>
+        <v>79482</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1295,7 +1295,7 @@
         <v>136876450</v>
       </c>
       <c r="B8" t="n">
-        <v>79480</v>
+        <v>79482</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1397,7 +1397,7 @@
         <v>136877256</v>
       </c>
       <c r="B9" t="n">
-        <v>79480</v>
+        <v>79482</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1499,7 +1499,7 @@
         <v>136876565</v>
       </c>
       <c r="B10" t="n">
-        <v>78883</v>
+        <v>78885</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1601,7 +1601,7 @@
         <v>136875998</v>
       </c>
       <c r="B11" t="n">
-        <v>83467</v>
+        <v>83469</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1707,7 +1707,7 @@
         <v>136875679</v>
       </c>
       <c r="B12" t="n">
-        <v>80099</v>
+        <v>80101</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1809,7 +1809,7 @@
         <v>136876728</v>
       </c>
       <c r="B13" t="n">
-        <v>80099</v>
+        <v>80101</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1911,7 +1911,7 @@
         <v>136875760</v>
       </c>
       <c r="B14" t="n">
-        <v>80599</v>
+        <v>80601</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2013,7 +2013,7 @@
         <v>136876098</v>
       </c>
       <c r="B15" t="n">
-        <v>80599</v>
+        <v>80601</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2115,7 +2115,7 @@
         <v>136876326</v>
       </c>
       <c r="B16" t="n">
-        <v>78480</v>
+        <v>78482</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -3536,7 +3536,7 @@
         <v>136876734</v>
       </c>
       <c r="B29" t="n">
-        <v>80070</v>
+        <v>80072</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3638,7 +3638,7 @@
         <v>136875725</v>
       </c>
       <c r="B30" t="n">
-        <v>79503</v>
+        <v>79505</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3740,7 +3740,7 @@
         <v>136876573</v>
       </c>
       <c r="B31" t="n">
-        <v>79503</v>
+        <v>79505</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>

--- a/artfynd/A 50182-2025 artfynd.xlsx
+++ b/artfynd/A 50182-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136876156</v>
       </c>
       <c r="B2" t="n">
-        <v>79148</v>
+        <v>79149</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>136876745</v>
       </c>
       <c r="B3" t="n">
-        <v>92388</v>
+        <v>92389</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         <v>136876592</v>
       </c>
       <c r="B4" t="n">
-        <v>92117</v>
+        <v>92118</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
         <v>136876789</v>
       </c>
       <c r="B5" t="n">
-        <v>92117</v>
+        <v>92118</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1091,7 +1091,7 @@
         <v>136876174</v>
       </c>
       <c r="B6" t="n">
-        <v>79482</v>
+        <v>79483</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1193,7 +1193,7 @@
         <v>136876238</v>
       </c>
       <c r="B7" t="n">
-        <v>79482</v>
+        <v>79483</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1295,7 +1295,7 @@
         <v>136876450</v>
       </c>
       <c r="B8" t="n">
-        <v>79482</v>
+        <v>79483</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1397,7 +1397,7 @@
         <v>136877256</v>
       </c>
       <c r="B9" t="n">
-        <v>79482</v>
+        <v>79483</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1499,7 +1499,7 @@
         <v>136876565</v>
       </c>
       <c r="B10" t="n">
-        <v>78885</v>
+        <v>78886</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1601,7 +1601,7 @@
         <v>136875998</v>
       </c>
       <c r="B11" t="n">
-        <v>83469</v>
+        <v>83470</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1707,7 +1707,7 @@
         <v>136875679</v>
       </c>
       <c r="B12" t="n">
-        <v>80101</v>
+        <v>80102</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1809,7 +1809,7 @@
         <v>136876728</v>
       </c>
       <c r="B13" t="n">
-        <v>80101</v>
+        <v>80102</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1911,7 +1911,7 @@
         <v>136875760</v>
       </c>
       <c r="B14" t="n">
-        <v>80601</v>
+        <v>80602</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2013,7 +2013,7 @@
         <v>136876098</v>
       </c>
       <c r="B15" t="n">
-        <v>80601</v>
+        <v>80602</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2115,7 +2115,7 @@
         <v>136876326</v>
       </c>
       <c r="B16" t="n">
-        <v>78482</v>
+        <v>78483</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -3536,7 +3536,7 @@
         <v>136876734</v>
       </c>
       <c r="B29" t="n">
-        <v>80072</v>
+        <v>80073</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3638,7 +3638,7 @@
         <v>136875725</v>
       </c>
       <c r="B30" t="n">
-        <v>79505</v>
+        <v>79506</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3740,7 +3740,7 @@
         <v>136876573</v>
       </c>
       <c r="B31" t="n">
-        <v>79505</v>
+        <v>79506</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>

--- a/artfynd/A 50182-2025 artfynd.xlsx
+++ b/artfynd/A 50182-2025 artfynd.xlsx
@@ -785,7 +785,7 @@
         <v>136876745</v>
       </c>
       <c r="B3" t="n">
-        <v>92389</v>
+        <v>92395</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         <v>136876592</v>
       </c>
       <c r="B4" t="n">
-        <v>92118</v>
+        <v>92124</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
         <v>136876789</v>
       </c>
       <c r="B5" t="n">
-        <v>92118</v>
+        <v>92124</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 50182-2025 artfynd.xlsx
+++ b/artfynd/A 50182-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136876156</v>
       </c>
       <c r="B2" t="n">
-        <v>79149</v>
+        <v>79151</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>136876745</v>
       </c>
       <c r="B3" t="n">
-        <v>92395</v>
+        <v>92399</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         <v>136876592</v>
       </c>
       <c r="B4" t="n">
-        <v>92124</v>
+        <v>92128</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
         <v>136876789</v>
       </c>
       <c r="B5" t="n">
-        <v>92124</v>
+        <v>92128</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1091,7 +1091,7 @@
         <v>136876174</v>
       </c>
       <c r="B6" t="n">
-        <v>79483</v>
+        <v>79485</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1193,7 +1193,7 @@
         <v>136876238</v>
       </c>
       <c r="B7" t="n">
-        <v>79483</v>
+        <v>79485</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1295,7 +1295,7 @@
         <v>136876450</v>
       </c>
       <c r="B8" t="n">
-        <v>79483</v>
+        <v>79485</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1397,7 +1397,7 @@
         <v>136877256</v>
       </c>
       <c r="B9" t="n">
-        <v>79483</v>
+        <v>79485</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1499,7 +1499,7 @@
         <v>136876565</v>
       </c>
       <c r="B10" t="n">
-        <v>78886</v>
+        <v>78888</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1601,7 +1601,7 @@
         <v>136875998</v>
       </c>
       <c r="B11" t="n">
-        <v>83470</v>
+        <v>83474</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1707,7 +1707,7 @@
         <v>136875679</v>
       </c>
       <c r="B12" t="n">
-        <v>80102</v>
+        <v>80104</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1809,7 +1809,7 @@
         <v>136876728</v>
       </c>
       <c r="B13" t="n">
-        <v>80102</v>
+        <v>80104</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1911,7 +1911,7 @@
         <v>136875760</v>
       </c>
       <c r="B14" t="n">
-        <v>80602</v>
+        <v>80604</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2013,7 +2013,7 @@
         <v>136876098</v>
       </c>
       <c r="B15" t="n">
-        <v>80602</v>
+        <v>80604</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2115,7 +2115,7 @@
         <v>136876326</v>
       </c>
       <c r="B16" t="n">
-        <v>78483</v>
+        <v>78485</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -3536,7 +3536,7 @@
         <v>136876734</v>
       </c>
       <c r="B29" t="n">
-        <v>80073</v>
+        <v>80075</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3638,7 +3638,7 @@
         <v>136875725</v>
       </c>
       <c r="B30" t="n">
-        <v>79506</v>
+        <v>79508</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3740,7 +3740,7 @@
         <v>136876573</v>
       </c>
       <c r="B31" t="n">
-        <v>79506</v>
+        <v>79508</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>

--- a/artfynd/A 50182-2025 artfynd.xlsx
+++ b/artfynd/A 50182-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136876156</v>
       </c>
       <c r="B2" t="n">
-        <v>79151</v>
+        <v>79154</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>136876745</v>
       </c>
       <c r="B3" t="n">
-        <v>92399</v>
+        <v>92401</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         <v>136876592</v>
       </c>
       <c r="B4" t="n">
-        <v>92128</v>
+        <v>92130</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
         <v>136876789</v>
       </c>
       <c r="B5" t="n">
-        <v>92128</v>
+        <v>92130</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1091,7 +1091,7 @@
         <v>136876174</v>
       </c>
       <c r="B6" t="n">
-        <v>79485</v>
+        <v>79488</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1193,7 +1193,7 @@
         <v>136876238</v>
       </c>
       <c r="B7" t="n">
-        <v>79485</v>
+        <v>79488</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1295,7 +1295,7 @@
         <v>136876450</v>
       </c>
       <c r="B8" t="n">
-        <v>79485</v>
+        <v>79488</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1397,7 +1397,7 @@
         <v>136877256</v>
       </c>
       <c r="B9" t="n">
-        <v>79485</v>
+        <v>79488</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1499,7 +1499,7 @@
         <v>136876565</v>
       </c>
       <c r="B10" t="n">
-        <v>78888</v>
+        <v>78891</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1601,7 +1601,7 @@
         <v>136875998</v>
       </c>
       <c r="B11" t="n">
-        <v>83474</v>
+        <v>83476</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1707,7 +1707,7 @@
         <v>136875679</v>
       </c>
       <c r="B12" t="n">
-        <v>80104</v>
+        <v>80107</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1809,7 +1809,7 @@
         <v>136876728</v>
       </c>
       <c r="B13" t="n">
-        <v>80104</v>
+        <v>80107</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1911,7 +1911,7 @@
         <v>136875760</v>
       </c>
       <c r="B14" t="n">
-        <v>80604</v>
+        <v>80607</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2013,7 +2013,7 @@
         <v>136876098</v>
       </c>
       <c r="B15" t="n">
-        <v>80604</v>
+        <v>80607</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2115,7 +2115,7 @@
         <v>136876326</v>
       </c>
       <c r="B16" t="n">
-        <v>78485</v>
+        <v>78488</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -3536,7 +3536,7 @@
         <v>136876734</v>
       </c>
       <c r="B29" t="n">
-        <v>80075</v>
+        <v>80078</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3638,7 +3638,7 @@
         <v>136875725</v>
       </c>
       <c r="B30" t="n">
-        <v>79508</v>
+        <v>79511</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3740,7 +3740,7 @@
         <v>136876573</v>
       </c>
       <c r="B31" t="n">
-        <v>79508</v>
+        <v>79511</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>

--- a/artfynd/A 50182-2025 artfynd.xlsx
+++ b/artfynd/A 50182-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136876156</v>
       </c>
       <c r="B2" t="n">
-        <v>79154</v>
+        <v>79167</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>136876745</v>
       </c>
       <c r="B3" t="n">
-        <v>92401</v>
+        <v>92414</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         <v>136876592</v>
       </c>
       <c r="B4" t="n">
-        <v>92130</v>
+        <v>92143</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
         <v>136876789</v>
       </c>
       <c r="B5" t="n">
-        <v>92130</v>
+        <v>92143</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1091,7 +1091,7 @@
         <v>136876174</v>
       </c>
       <c r="B6" t="n">
-        <v>79488</v>
+        <v>79501</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1193,7 +1193,7 @@
         <v>136876238</v>
       </c>
       <c r="B7" t="n">
-        <v>79488</v>
+        <v>79501</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1295,7 +1295,7 @@
         <v>136876450</v>
       </c>
       <c r="B8" t="n">
-        <v>79488</v>
+        <v>79501</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1397,7 +1397,7 @@
         <v>136877256</v>
       </c>
       <c r="B9" t="n">
-        <v>79488</v>
+        <v>79501</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1499,7 +1499,7 @@
         <v>136876565</v>
       </c>
       <c r="B10" t="n">
-        <v>78891</v>
+        <v>78904</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1601,7 +1601,7 @@
         <v>136875998</v>
       </c>
       <c r="B11" t="n">
-        <v>83476</v>
+        <v>83489</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1707,7 +1707,7 @@
         <v>136875679</v>
       </c>
       <c r="B12" t="n">
-        <v>80107</v>
+        <v>80120</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1809,7 +1809,7 @@
         <v>136876728</v>
       </c>
       <c r="B13" t="n">
-        <v>80107</v>
+        <v>80120</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1911,7 +1911,7 @@
         <v>136875760</v>
       </c>
       <c r="B14" t="n">
-        <v>80607</v>
+        <v>80620</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2013,7 +2013,7 @@
         <v>136876098</v>
       </c>
       <c r="B15" t="n">
-        <v>80607</v>
+        <v>80620</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2115,7 +2115,7 @@
         <v>136876326</v>
       </c>
       <c r="B16" t="n">
-        <v>78488</v>
+        <v>78501</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2538,7 +2538,7 @@
         <v>136875592</v>
       </c>
       <c r="B20" t="n">
-        <v>58008</v>
+        <v>58021</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2650,7 +2650,7 @@
         <v>136876019</v>
       </c>
       <c r="B21" t="n">
-        <v>58008</v>
+        <v>58021</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2762,7 +2762,7 @@
         <v>136876076</v>
       </c>
       <c r="B22" t="n">
-        <v>58008</v>
+        <v>58021</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2874,7 +2874,7 @@
         <v>136876706</v>
       </c>
       <c r="B23" t="n">
-        <v>58008</v>
+        <v>58021</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2986,7 +2986,7 @@
         <v>136876886</v>
       </c>
       <c r="B24" t="n">
-        <v>58008</v>
+        <v>58021</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3098,7 +3098,7 @@
         <v>136877183</v>
       </c>
       <c r="B25" t="n">
-        <v>58008</v>
+        <v>58021</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3210,7 +3210,7 @@
         <v>136877310</v>
       </c>
       <c r="B26" t="n">
-        <v>58008</v>
+        <v>58021</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3322,7 +3322,7 @@
         <v>136877341</v>
       </c>
       <c r="B27" t="n">
-        <v>58008</v>
+        <v>58021</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3434,7 +3434,7 @@
         <v>136875986</v>
       </c>
       <c r="B28" t="n">
-        <v>58112</v>
+        <v>58125</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3536,7 +3536,7 @@
         <v>136876734</v>
       </c>
       <c r="B29" t="n">
-        <v>80078</v>
+        <v>80091</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3638,7 +3638,7 @@
         <v>136875725</v>
       </c>
       <c r="B30" t="n">
-        <v>79511</v>
+        <v>79524</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3740,7 +3740,7 @@
         <v>136876573</v>
       </c>
       <c r="B31" t="n">
-        <v>79511</v>
+        <v>79524</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>

--- a/artfynd/A 50182-2025 artfynd.xlsx
+++ b/artfynd/A 50182-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136876156</v>
       </c>
       <c r="B2" t="n">
-        <v>79167</v>
+        <v>79169</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>136876745</v>
       </c>
       <c r="B3" t="n">
-        <v>92414</v>
+        <v>92416</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         <v>136876592</v>
       </c>
       <c r="B4" t="n">
-        <v>92143</v>
+        <v>92145</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
         <v>136876789</v>
       </c>
       <c r="B5" t="n">
-        <v>92143</v>
+        <v>92145</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1091,7 +1091,7 @@
         <v>136876174</v>
       </c>
       <c r="B6" t="n">
-        <v>79501</v>
+        <v>79503</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1193,7 +1193,7 @@
         <v>136876238</v>
       </c>
       <c r="B7" t="n">
-        <v>79501</v>
+        <v>79503</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1295,7 +1295,7 @@
         <v>136876450</v>
       </c>
       <c r="B8" t="n">
-        <v>79501</v>
+        <v>79503</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1397,7 +1397,7 @@
         <v>136877256</v>
       </c>
       <c r="B9" t="n">
-        <v>79501</v>
+        <v>79503</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1499,7 +1499,7 @@
         <v>136876565</v>
       </c>
       <c r="B10" t="n">
-        <v>78904</v>
+        <v>78906</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1601,7 +1601,7 @@
         <v>136875998</v>
       </c>
       <c r="B11" t="n">
-        <v>83489</v>
+        <v>83491</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1707,7 +1707,7 @@
         <v>136875679</v>
       </c>
       <c r="B12" t="n">
-        <v>80120</v>
+        <v>80122</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1809,7 +1809,7 @@
         <v>136876728</v>
       </c>
       <c r="B13" t="n">
-        <v>80120</v>
+        <v>80122</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1911,7 +1911,7 @@
         <v>136875760</v>
       </c>
       <c r="B14" t="n">
-        <v>80620</v>
+        <v>80622</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2013,7 +2013,7 @@
         <v>136876098</v>
       </c>
       <c r="B15" t="n">
-        <v>80620</v>
+        <v>80622</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2115,7 +2115,7 @@
         <v>136876326</v>
       </c>
       <c r="B16" t="n">
-        <v>78501</v>
+        <v>78503</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2538,7 +2538,7 @@
         <v>136875592</v>
       </c>
       <c r="B20" t="n">
-        <v>58021</v>
+        <v>58023</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2650,7 +2650,7 @@
         <v>136876019</v>
       </c>
       <c r="B21" t="n">
-        <v>58021</v>
+        <v>58023</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2762,7 +2762,7 @@
         <v>136876076</v>
       </c>
       <c r="B22" t="n">
-        <v>58021</v>
+        <v>58023</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2874,7 +2874,7 @@
         <v>136876706</v>
       </c>
       <c r="B23" t="n">
-        <v>58021</v>
+        <v>58023</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2986,7 +2986,7 @@
         <v>136876886</v>
       </c>
       <c r="B24" t="n">
-        <v>58021</v>
+        <v>58023</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3098,7 +3098,7 @@
         <v>136877183</v>
       </c>
       <c r="B25" t="n">
-        <v>58021</v>
+        <v>58023</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3210,7 +3210,7 @@
         <v>136877310</v>
       </c>
       <c r="B26" t="n">
-        <v>58021</v>
+        <v>58023</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3322,7 +3322,7 @@
         <v>136877341</v>
       </c>
       <c r="B27" t="n">
-        <v>58021</v>
+        <v>58023</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3434,7 +3434,7 @@
         <v>136875986</v>
       </c>
       <c r="B28" t="n">
-        <v>58125</v>
+        <v>58127</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3536,7 +3536,7 @@
         <v>136876734</v>
       </c>
       <c r="B29" t="n">
-        <v>80091</v>
+        <v>80093</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3638,7 +3638,7 @@
         <v>136875725</v>
       </c>
       <c r="B30" t="n">
-        <v>79524</v>
+        <v>79526</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3740,7 +3740,7 @@
         <v>136876573</v>
       </c>
       <c r="B31" t="n">
-        <v>79524</v>
+        <v>79526</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>

--- a/artfynd/A 50182-2025 artfynd.xlsx
+++ b/artfynd/A 50182-2025 artfynd.xlsx
@@ -2564,11 +2564,7 @@
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+      <c r="M20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
           <t>Över-Dammtjärnen, Över-Dammtjärnen, Hjd</t>
@@ -2676,11 +2672,7 @@
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+      <c r="M21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
           <t>Neder-Dammtjärnen, Neder-Dammtjärnen, Hjd</t>
@@ -2788,11 +2780,7 @@
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
+      <c r="M22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>Neder-Dammtjärnen, Neder-Dammtjärnen, Hjd</t>
@@ -2900,11 +2888,7 @@
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+      <c r="M23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Neder-Dammtjärnen, Neder-Dammtjärnen, Hjd</t>
@@ -3012,11 +2996,7 @@
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
+      <c r="M24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
           <t>Neder-Dammtjärnen, Neder-Dammtjärnen, Hjd</t>
@@ -3124,16 +3104,8 @@
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="L25" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+      <c r="L25" t="inlineStr"/>
+      <c r="M25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
           <t>Neder-Dammtjärnen, Neder-Dammtjärnen, Hjd</t>
@@ -3236,11 +3208,7 @@
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+      <c r="M26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
           <t>Neder-Dammtjärnen, Neder-Dammtjärnen, Hjd</t>
@@ -3348,11 +3316,7 @@
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
+      <c r="M27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
           <t>Över-Dammtjärnen, Över-Dammtjärnen, Hjd</t>

--- a/artfynd/A 50182-2025 artfynd.xlsx
+++ b/artfynd/A 50182-2025 artfynd.xlsx
@@ -785,7 +785,7 @@
         <v>136876745</v>
       </c>
       <c r="B3" t="n">
-        <v>92416</v>
+        <v>92419</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         <v>136876592</v>
       </c>
       <c r="B4" t="n">
-        <v>92145</v>
+        <v>92148</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
         <v>136876789</v>
       </c>
       <c r="B5" t="n">
-        <v>92145</v>
+        <v>92148</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1601,7 +1601,7 @@
         <v>136875998</v>
       </c>
       <c r="B11" t="n">
-        <v>83491</v>
+        <v>83494</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 50182-2025 artfynd.xlsx
+++ b/artfynd/A 50182-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136876156</v>
       </c>
       <c r="B2" t="n">
-        <v>79169</v>
+        <v>79179</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>136876745</v>
       </c>
       <c r="B3" t="n">
-        <v>92419</v>
+        <v>92429</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         <v>136876592</v>
       </c>
       <c r="B4" t="n">
-        <v>92148</v>
+        <v>92158</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
         <v>136876789</v>
       </c>
       <c r="B5" t="n">
-        <v>92148</v>
+        <v>92158</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1091,7 +1091,7 @@
         <v>136876174</v>
       </c>
       <c r="B6" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1193,7 +1193,7 @@
         <v>136876238</v>
       </c>
       <c r="B7" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1295,7 +1295,7 @@
         <v>136876450</v>
       </c>
       <c r="B8" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1397,7 +1397,7 @@
         <v>136877256</v>
       </c>
       <c r="B9" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1499,7 +1499,7 @@
         <v>136876565</v>
       </c>
       <c r="B10" t="n">
-        <v>78906</v>
+        <v>78916</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1601,7 +1601,7 @@
         <v>136875998</v>
       </c>
       <c r="B11" t="n">
-        <v>83494</v>
+        <v>83504</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1707,7 +1707,7 @@
         <v>136875679</v>
       </c>
       <c r="B12" t="n">
-        <v>80122</v>
+        <v>80132</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1809,7 +1809,7 @@
         <v>136876728</v>
       </c>
       <c r="B13" t="n">
-        <v>80122</v>
+        <v>80132</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1911,7 +1911,7 @@
         <v>136875760</v>
       </c>
       <c r="B14" t="n">
-        <v>80622</v>
+        <v>80632</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2013,7 +2013,7 @@
         <v>136876098</v>
       </c>
       <c r="B15" t="n">
-        <v>80622</v>
+        <v>80632</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2115,7 +2115,7 @@
         <v>136876326</v>
       </c>
       <c r="B16" t="n">
-        <v>78503</v>
+        <v>78513</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2538,7 +2538,7 @@
         <v>136875592</v>
       </c>
       <c r="B20" t="n">
-        <v>58023</v>
+        <v>58033</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2646,7 +2646,7 @@
         <v>136876019</v>
       </c>
       <c r="B21" t="n">
-        <v>58023</v>
+        <v>58033</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2754,7 +2754,7 @@
         <v>136876076</v>
       </c>
       <c r="B22" t="n">
-        <v>58023</v>
+        <v>58033</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2862,7 +2862,7 @@
         <v>136876706</v>
       </c>
       <c r="B23" t="n">
-        <v>58023</v>
+        <v>58033</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2970,7 +2970,7 @@
         <v>136876886</v>
       </c>
       <c r="B24" t="n">
-        <v>58023</v>
+        <v>58033</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3078,7 +3078,7 @@
         <v>136877183</v>
       </c>
       <c r="B25" t="n">
-        <v>58023</v>
+        <v>58033</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3182,7 +3182,7 @@
         <v>136877310</v>
       </c>
       <c r="B26" t="n">
-        <v>58023</v>
+        <v>58033</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3290,7 +3290,7 @@
         <v>136877341</v>
       </c>
       <c r="B27" t="n">
-        <v>58023</v>
+        <v>58033</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3398,7 +3398,7 @@
         <v>136875986</v>
       </c>
       <c r="B28" t="n">
-        <v>58127</v>
+        <v>58137</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3500,7 +3500,7 @@
         <v>136876734</v>
       </c>
       <c r="B29" t="n">
-        <v>80093</v>
+        <v>80103</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3602,7 +3602,7 @@
         <v>136875725</v>
       </c>
       <c r="B30" t="n">
-        <v>79526</v>
+        <v>79536</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3704,7 +3704,7 @@
         <v>136876573</v>
       </c>
       <c r="B31" t="n">
-        <v>79526</v>
+        <v>79536</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>

--- a/artfynd/A 50182-2025 artfynd.xlsx
+++ b/artfynd/A 50182-2025 artfynd.xlsx
@@ -785,7 +785,7 @@
         <v>136876745</v>
       </c>
       <c r="B3" t="n">
-        <v>92429</v>
+        <v>92430</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         <v>136876592</v>
       </c>
       <c r="B4" t="n">
-        <v>92158</v>
+        <v>92159</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
         <v>136876789</v>
       </c>
       <c r="B5" t="n">
-        <v>92158</v>
+        <v>92159</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 50182-2025 artfynd.xlsx
+++ b/artfynd/A 50182-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136876156</v>
       </c>
       <c r="B2" t="n">
-        <v>79179</v>
+        <v>79182</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>136876745</v>
       </c>
       <c r="B3" t="n">
-        <v>92430</v>
+        <v>92433</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         <v>136876592</v>
       </c>
       <c r="B4" t="n">
-        <v>92159</v>
+        <v>92162</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
         <v>136876789</v>
       </c>
       <c r="B5" t="n">
-        <v>92159</v>
+        <v>92162</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1091,7 +1091,7 @@
         <v>136876174</v>
       </c>
       <c r="B6" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1193,7 +1193,7 @@
         <v>136876238</v>
       </c>
       <c r="B7" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1295,7 +1295,7 @@
         <v>136876450</v>
       </c>
       <c r="B8" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1397,7 +1397,7 @@
         <v>136877256</v>
       </c>
       <c r="B9" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1499,7 +1499,7 @@
         <v>136876565</v>
       </c>
       <c r="B10" t="n">
-        <v>78916</v>
+        <v>78919</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1601,7 +1601,7 @@
         <v>136875998</v>
       </c>
       <c r="B11" t="n">
-        <v>83504</v>
+        <v>83507</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1707,7 +1707,7 @@
         <v>136875679</v>
       </c>
       <c r="B12" t="n">
-        <v>80132</v>
+        <v>80135</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1809,7 +1809,7 @@
         <v>136876728</v>
       </c>
       <c r="B13" t="n">
-        <v>80132</v>
+        <v>80135</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1911,7 +1911,7 @@
         <v>136875760</v>
       </c>
       <c r="B14" t="n">
-        <v>80632</v>
+        <v>80635</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2013,7 +2013,7 @@
         <v>136876098</v>
       </c>
       <c r="B15" t="n">
-        <v>80632</v>
+        <v>80635</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2115,7 +2115,7 @@
         <v>136876326</v>
       </c>
       <c r="B16" t="n">
-        <v>78513</v>
+        <v>78516</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2538,7 +2538,7 @@
         <v>136875592</v>
       </c>
       <c r="B20" t="n">
-        <v>58033</v>
+        <v>58034</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2646,7 +2646,7 @@
         <v>136876019</v>
       </c>
       <c r="B21" t="n">
-        <v>58033</v>
+        <v>58034</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2754,7 +2754,7 @@
         <v>136876076</v>
       </c>
       <c r="B22" t="n">
-        <v>58033</v>
+        <v>58034</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2862,7 +2862,7 @@
         <v>136876706</v>
       </c>
       <c r="B23" t="n">
-        <v>58033</v>
+        <v>58034</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2970,7 +2970,7 @@
         <v>136876886</v>
       </c>
       <c r="B24" t="n">
-        <v>58033</v>
+        <v>58034</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3078,7 +3078,7 @@
         <v>136877183</v>
       </c>
       <c r="B25" t="n">
-        <v>58033</v>
+        <v>58034</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3182,7 +3182,7 @@
         <v>136877310</v>
       </c>
       <c r="B26" t="n">
-        <v>58033</v>
+        <v>58034</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3290,7 +3290,7 @@
         <v>136877341</v>
       </c>
       <c r="B27" t="n">
-        <v>58033</v>
+        <v>58034</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3398,7 +3398,7 @@
         <v>136875986</v>
       </c>
       <c r="B28" t="n">
-        <v>58137</v>
+        <v>58138</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3500,7 +3500,7 @@
         <v>136876734</v>
       </c>
       <c r="B29" t="n">
-        <v>80103</v>
+        <v>80106</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3602,7 +3602,7 @@
         <v>136875725</v>
       </c>
       <c r="B30" t="n">
-        <v>79536</v>
+        <v>79539</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3704,7 +3704,7 @@
         <v>136876573</v>
       </c>
       <c r="B31" t="n">
-        <v>79536</v>
+        <v>79539</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>

--- a/artfynd/A 50182-2025 artfynd.xlsx
+++ b/artfynd/A 50182-2025 artfynd.xlsx
@@ -785,7 +785,7 @@
         <v>136876745</v>
       </c>
       <c r="B3" t="n">
-        <v>92433</v>
+        <v>92435</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         <v>136876592</v>
       </c>
       <c r="B4" t="n">
-        <v>92162</v>
+        <v>92164</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
         <v>136876789</v>
       </c>
       <c r="B5" t="n">
-        <v>92162</v>
+        <v>92164</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 50182-2025 artfynd.xlsx
+++ b/artfynd/A 50182-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136876156</v>
       </c>
       <c r="B2" t="n">
-        <v>79182</v>
+        <v>79187</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>136876745</v>
       </c>
       <c r="B3" t="n">
-        <v>92435</v>
+        <v>92440</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         <v>136876592</v>
       </c>
       <c r="B4" t="n">
-        <v>92164</v>
+        <v>92169</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
         <v>136876789</v>
       </c>
       <c r="B5" t="n">
-        <v>92164</v>
+        <v>92169</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1091,7 +1091,7 @@
         <v>136876174</v>
       </c>
       <c r="B6" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1193,7 +1193,7 @@
         <v>136876238</v>
       </c>
       <c r="B7" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1295,7 +1295,7 @@
         <v>136876450</v>
       </c>
       <c r="B8" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1397,7 +1397,7 @@
         <v>136877256</v>
       </c>
       <c r="B9" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1499,7 +1499,7 @@
         <v>136876565</v>
       </c>
       <c r="B10" t="n">
-        <v>78919</v>
+        <v>78924</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1601,7 +1601,7 @@
         <v>136875998</v>
       </c>
       <c r="B11" t="n">
-        <v>83507</v>
+        <v>83512</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1707,7 +1707,7 @@
         <v>136875679</v>
       </c>
       <c r="B12" t="n">
-        <v>80135</v>
+        <v>80140</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1809,7 +1809,7 @@
         <v>136876728</v>
       </c>
       <c r="B13" t="n">
-        <v>80135</v>
+        <v>80140</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1911,7 +1911,7 @@
         <v>136875760</v>
       </c>
       <c r="B14" t="n">
-        <v>80635</v>
+        <v>80640</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2013,7 +2013,7 @@
         <v>136876098</v>
       </c>
       <c r="B15" t="n">
-        <v>80635</v>
+        <v>80640</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2115,7 +2115,7 @@
         <v>136876326</v>
       </c>
       <c r="B16" t="n">
-        <v>78516</v>
+        <v>78521</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2538,7 +2538,7 @@
         <v>136875592</v>
       </c>
       <c r="B20" t="n">
-        <v>58034</v>
+        <v>58035</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2646,7 +2646,7 @@
         <v>136876019</v>
       </c>
       <c r="B21" t="n">
-        <v>58034</v>
+        <v>58035</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2754,7 +2754,7 @@
         <v>136876076</v>
       </c>
       <c r="B22" t="n">
-        <v>58034</v>
+        <v>58035</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2862,7 +2862,7 @@
         <v>136876706</v>
       </c>
       <c r="B23" t="n">
-        <v>58034</v>
+        <v>58035</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2970,7 +2970,7 @@
         <v>136876886</v>
       </c>
       <c r="B24" t="n">
-        <v>58034</v>
+        <v>58035</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3078,7 +3078,7 @@
         <v>136877183</v>
       </c>
       <c r="B25" t="n">
-        <v>58034</v>
+        <v>58035</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3182,7 +3182,7 @@
         <v>136877310</v>
       </c>
       <c r="B26" t="n">
-        <v>58034</v>
+        <v>58035</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3290,7 +3290,7 @@
         <v>136877341</v>
       </c>
       <c r="B27" t="n">
-        <v>58034</v>
+        <v>58035</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3398,7 +3398,7 @@
         <v>136875986</v>
       </c>
       <c r="B28" t="n">
-        <v>58138</v>
+        <v>58139</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3500,7 +3500,7 @@
         <v>136876734</v>
       </c>
       <c r="B29" t="n">
-        <v>80106</v>
+        <v>80111</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3602,7 +3602,7 @@
         <v>136875725</v>
       </c>
       <c r="B30" t="n">
-        <v>79539</v>
+        <v>79544</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3704,7 +3704,7 @@
         <v>136876573</v>
       </c>
       <c r="B31" t="n">
-        <v>79539</v>
+        <v>79544</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>

--- a/artfynd/A 50182-2025 artfynd.xlsx
+++ b/artfynd/A 50182-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136876156</v>
       </c>
       <c r="B2" t="n">
-        <v>79187</v>
+        <v>79198</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>136876745</v>
       </c>
       <c r="B3" t="n">
-        <v>92440</v>
+        <v>92452</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         <v>136876592</v>
       </c>
       <c r="B4" t="n">
-        <v>92169</v>
+        <v>92181</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
         <v>136876789</v>
       </c>
       <c r="B5" t="n">
-        <v>92169</v>
+        <v>92181</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1091,7 +1091,7 @@
         <v>136876174</v>
       </c>
       <c r="B6" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1193,7 +1193,7 @@
         <v>136876238</v>
       </c>
       <c r="B7" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1295,7 +1295,7 @@
         <v>136876450</v>
       </c>
       <c r="B8" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1397,7 +1397,7 @@
         <v>136877256</v>
       </c>
       <c r="B9" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1499,7 +1499,7 @@
         <v>136876565</v>
       </c>
       <c r="B10" t="n">
-        <v>78924</v>
+        <v>78935</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1601,7 +1601,7 @@
         <v>136875998</v>
       </c>
       <c r="B11" t="n">
-        <v>83512</v>
+        <v>83523</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1707,7 +1707,7 @@
         <v>136875679</v>
       </c>
       <c r="B12" t="n">
-        <v>80140</v>
+        <v>80151</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1809,7 +1809,7 @@
         <v>136876728</v>
       </c>
       <c r="B13" t="n">
-        <v>80140</v>
+        <v>80151</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1911,7 +1911,7 @@
         <v>136875760</v>
       </c>
       <c r="B14" t="n">
-        <v>80640</v>
+        <v>80651</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2013,7 +2013,7 @@
         <v>136876098</v>
       </c>
       <c r="B15" t="n">
-        <v>80640</v>
+        <v>80651</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2115,7 +2115,7 @@
         <v>136876326</v>
       </c>
       <c r="B16" t="n">
-        <v>78521</v>
+        <v>78532</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -3500,7 +3500,7 @@
         <v>136876734</v>
       </c>
       <c r="B29" t="n">
-        <v>80111</v>
+        <v>80122</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3602,7 +3602,7 @@
         <v>136875725</v>
       </c>
       <c r="B30" t="n">
-        <v>79544</v>
+        <v>79555</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3704,7 +3704,7 @@
         <v>136876573</v>
       </c>
       <c r="B31" t="n">
-        <v>79544</v>
+        <v>79555</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>

--- a/artfynd/A 50182-2025 artfynd.xlsx
+++ b/artfynd/A 50182-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136876156</v>
       </c>
       <c r="B2" t="n">
-        <v>79198</v>
+        <v>79199</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>136876745</v>
       </c>
       <c r="B3" t="n">
-        <v>92452</v>
+        <v>92453</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         <v>136876592</v>
       </c>
       <c r="B4" t="n">
-        <v>92181</v>
+        <v>92182</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
         <v>136876789</v>
       </c>
       <c r="B5" t="n">
-        <v>92181</v>
+        <v>92182</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1091,7 +1091,7 @@
         <v>136876174</v>
       </c>
       <c r="B6" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1193,7 +1193,7 @@
         <v>136876238</v>
       </c>
       <c r="B7" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1295,7 +1295,7 @@
         <v>136876450</v>
       </c>
       <c r="B8" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1397,7 +1397,7 @@
         <v>136877256</v>
       </c>
       <c r="B9" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1499,7 +1499,7 @@
         <v>136876565</v>
       </c>
       <c r="B10" t="n">
-        <v>78935</v>
+        <v>78936</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1601,7 +1601,7 @@
         <v>136875998</v>
       </c>
       <c r="B11" t="n">
-        <v>83523</v>
+        <v>83524</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1707,7 +1707,7 @@
         <v>136875679</v>
       </c>
       <c r="B12" t="n">
-        <v>80151</v>
+        <v>80152</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1809,7 +1809,7 @@
         <v>136876728</v>
       </c>
       <c r="B13" t="n">
-        <v>80151</v>
+        <v>80152</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1911,7 +1911,7 @@
         <v>136875760</v>
       </c>
       <c r="B14" t="n">
-        <v>80651</v>
+        <v>80652</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2013,7 +2013,7 @@
         <v>136876098</v>
       </c>
       <c r="B15" t="n">
-        <v>80651</v>
+        <v>80652</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2115,7 +2115,7 @@
         <v>136876326</v>
       </c>
       <c r="B16" t="n">
-        <v>78532</v>
+        <v>78533</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -3500,7 +3500,7 @@
         <v>136876734</v>
       </c>
       <c r="B29" t="n">
-        <v>80122</v>
+        <v>80123</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3602,7 +3602,7 @@
         <v>136875725</v>
       </c>
       <c r="B30" t="n">
-        <v>79555</v>
+        <v>79556</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3704,7 +3704,7 @@
         <v>136876573</v>
       </c>
       <c r="B31" t="n">
-        <v>79555</v>
+        <v>79556</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>

--- a/artfynd/A 50182-2025 artfynd.xlsx
+++ b/artfynd/A 50182-2025 artfynd.xlsx
@@ -1601,7 +1601,7 @@
         <v>136875998</v>
       </c>
       <c r="B11" t="n">
-        <v>83524</v>
+        <v>83526</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
